--- a/plantillas/Opiniones_Distrito.xlsx
+++ b/plantillas/Opiniones_Distrito.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FCB932-7DCF-40D8-BF73-70605AB2AC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D34291E-D26E-4EDC-A544-8655C0C179DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,8 @@
     <t>Opiniones Nulas SEI: Vía Remota</t>
   </si>
   <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
+    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
+SICOVACC 2026</t>
   </si>
 </sst>
 </file>
@@ -121,14 +122,16 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -197,14 +200,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -555,7 +558,7 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
     </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>9</v>
       </c>
@@ -597,21 +600,21 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
     </row>
-    <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="5"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9"/>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -624,22 +627,22 @@
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>2</v>
       </c>
     </row>

--- a/plantillas/Opiniones_Distrito.xlsx
+++ b/plantillas/Opiniones_Distrito.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D34291E-D26E-4EDC-A544-8655C0C179DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA10A060-915F-45E6-96FE-23B69929BDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
   </si>
   <si>
     <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
-SICOVACC 2026</t>
+SICOVACC</t>
   </si>
 </sst>
 </file>
